--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/61.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/61.xlsx
@@ -426,13 +426,13 @@
         <v>-14.11140432063964</v>
       </c>
       <c r="E2">
-        <v>-9.663145208137093</v>
+        <v>-9.407005661315242</v>
       </c>
       <c r="F2">
-        <v>-2.647589106807356</v>
+        <v>-2.654710581369224</v>
       </c>
       <c r="G2">
-        <v>-11.68900445200307</v>
+        <v>-11.29016978870492</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-13.4717022315405</v>
       </c>
       <c r="E3">
-        <v>-12.15886874629637</v>
+        <v>-9.182103528198303</v>
       </c>
       <c r="F3">
-        <v>-2.711706400518843</v>
+        <v>-2.484355996616102</v>
       </c>
       <c r="G3">
-        <v>-10.64886083847392</v>
+        <v>-10.71942842718902</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-12.79920571192019</v>
       </c>
       <c r="E4">
-        <v>-11.6135499062927</v>
+        <v>-9.606865333169766</v>
       </c>
       <c r="F4">
-        <v>-2.5494822418242</v>
+        <v>-2.625534653075222</v>
       </c>
       <c r="G4">
-        <v>-9.229709418881304</v>
+        <v>-10.61936718826455</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-12.16859585023628</v>
       </c>
       <c r="E5">
-        <v>-12.9825981682916</v>
+        <v>-10.93782912876416</v>
       </c>
       <c r="F5">
-        <v>-2.774734391095649</v>
+        <v>-2.534109399563046</v>
       </c>
       <c r="G5">
-        <v>-10.09951884332388</v>
+        <v>-9.44862255321115</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-11.59031507149707</v>
       </c>
       <c r="E6">
-        <v>-13.31465305337804</v>
+        <v>-11.15230671471545</v>
       </c>
       <c r="F6">
-        <v>-2.710220309398221</v>
+        <v>-2.264767395277592</v>
       </c>
       <c r="G6">
-        <v>-10.39797776587133</v>
+        <v>-9.525903928279897</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-11.0722519297318</v>
       </c>
       <c r="E7">
-        <v>-14.6102313530765</v>
+        <v>-12.4112813590099</v>
       </c>
       <c r="F7">
-        <v>-2.758231655697077</v>
+        <v>-2.377218270207625</v>
       </c>
       <c r="G7">
-        <v>-7.777095004977736</v>
+        <v>-9.691199467055707</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-10.63051605665599</v>
       </c>
       <c r="E8">
-        <v>-14.88471574810342</v>
+        <v>-12.91298646584569</v>
       </c>
       <c r="F8">
-        <v>-2.167664511586629</v>
+        <v>-2.251121699051276</v>
       </c>
       <c r="G8">
-        <v>-8.819698353842567</v>
+        <v>-8.962531841134423</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-10.26133659729275</v>
       </c>
       <c r="E9">
-        <v>-16.23156995899073</v>
+        <v>-13.73963675357588</v>
       </c>
       <c r="F9">
-        <v>-2.182855941386569</v>
+        <v>-2.33194716327723</v>
       </c>
       <c r="G9">
-        <v>-8.813544049685062</v>
+        <v>-8.644606910816053</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-9.98051798975821</v>
       </c>
       <c r="E10">
-        <v>-15.68217549238016</v>
+        <v>-14.22732170488393</v>
       </c>
       <c r="F10">
-        <v>-2.816786462298766</v>
+        <v>-1.855042795607109</v>
       </c>
       <c r="G10">
-        <v>-8.028895098694703</v>
+        <v>-8.061537077711916</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-9.781667383936716</v>
       </c>
       <c r="E11">
-        <v>-16.66223236559419</v>
+        <v>-15.27016134174029</v>
       </c>
       <c r="F11">
-        <v>-1.991560228690676</v>
+        <v>-2.023790347598799</v>
       </c>
       <c r="G11">
-        <v>-8.208932496756887</v>
+        <v>-7.314224459313456</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-9.682316137358336</v>
       </c>
       <c r="E12">
-        <v>-15.29176669123089</v>
+        <v>-14.87324059496799</v>
       </c>
       <c r="F12">
-        <v>-1.762581254474031</v>
+        <v>-1.842789584984899</v>
       </c>
       <c r="G12">
-        <v>-6.76139645971056</v>
+        <v>-7.585129711337556</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-9.674157655795783</v>
       </c>
       <c r="E13">
-        <v>-16.52670419549263</v>
+        <v>-16.10796978942538</v>
       </c>
       <c r="F13">
-        <v>-1.962215313446504</v>
+        <v>-1.88571558379797</v>
       </c>
       <c r="G13">
-        <v>-6.68213206786379</v>
+        <v>-6.585285368657951</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-9.766920298779283</v>
       </c>
       <c r="E14">
-        <v>-16.96098485282822</v>
+        <v>-16.80105273629933</v>
       </c>
       <c r="F14">
-        <v>-2.146109563398383</v>
+        <v>-1.735729725112285</v>
       </c>
       <c r="G14">
-        <v>-7.089309305920911</v>
+        <v>-6.588874000022521</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-9.941857054382846</v>
       </c>
       <c r="E15">
-        <v>-18.97698449698493</v>
+        <v>-17.24256989509917</v>
       </c>
       <c r="F15">
-        <v>-1.190766691628158</v>
+        <v>-1.348807594938664</v>
       </c>
       <c r="G15">
-        <v>-6.313281015514812</v>
+        <v>-5.520802624324076</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-10.18808517564039</v>
       </c>
       <c r="E16">
-        <v>-19.14434783936041</v>
+        <v>-18.09388225227513</v>
       </c>
       <c r="F16">
-        <v>-0.8756507613988092</v>
+        <v>-1.161850042331233</v>
       </c>
       <c r="G16">
-        <v>-5.066241547963367</v>
+        <v>-5.503898978800557</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-10.47376941583702</v>
       </c>
       <c r="E17">
-        <v>-18.66087889735351</v>
+        <v>-19.06288964891044</v>
       </c>
       <c r="F17">
-        <v>-1.399441552434784</v>
+        <v>-0.7058677501536197</v>
       </c>
       <c r="G17">
-        <v>-6.701243847262003</v>
+        <v>-4.947184398734557</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-10.77132740338571</v>
       </c>
       <c r="E18">
-        <v>-19.19211418319332</v>
+        <v>-20.09191291156941</v>
       </c>
       <c r="F18">
-        <v>-0.2899502757798075</v>
+        <v>-0.6030027428087826</v>
       </c>
       <c r="G18">
-        <v>-5.219367521336816</v>
+        <v>-5.182825719674341</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-11.04661606373084</v>
       </c>
       <c r="E19">
-        <v>-21.07655260047919</v>
+        <v>-20.04072756986071</v>
       </c>
       <c r="F19">
-        <v>-0.5315245763560189</v>
+        <v>-0.4092616895398259</v>
       </c>
       <c r="G19">
-        <v>-5.198471357892936</v>
+        <v>-5.686819862027447</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-11.27183027521088</v>
       </c>
       <c r="E20">
-        <v>-23.2122216987626</v>
+        <v>-20.62825178761586</v>
       </c>
       <c r="F20">
-        <v>-0.6832756859770688</v>
+        <v>-0.2919723206100411</v>
       </c>
       <c r="G20">
-        <v>-5.971043438756036</v>
+        <v>-5.278788503221195</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-11.42636182014557</v>
       </c>
       <c r="E21">
-        <v>-22.80941846425433</v>
+        <v>-21.77973857286425</v>
       </c>
       <c r="F21">
-        <v>-0.2555183563150433</v>
+        <v>0.04721679471206407</v>
       </c>
       <c r="G21">
-        <v>-6.443799273400579</v>
+        <v>-5.569543786298765</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-11.49581373332507</v>
       </c>
       <c r="E22">
-        <v>-21.50683914374002</v>
+        <v>-22.29424114724572</v>
       </c>
       <c r="F22">
-        <v>0.4816234295163612</v>
+        <v>0.2681788292044154</v>
       </c>
       <c r="G22">
-        <v>-7.059266105152025</v>
+        <v>-5.806231239628959</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-11.48081400879124</v>
       </c>
       <c r="E23">
-        <v>-22.54119242030601</v>
+        <v>-21.72693203746081</v>
       </c>
       <c r="F23">
-        <v>0.2082787539405803</v>
+        <v>0.574056806157744</v>
       </c>
       <c r="G23">
-        <v>-6.15462312054524</v>
+        <v>-6.310715342721877</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-11.38239760264065</v>
       </c>
       <c r="E24">
-        <v>-23.27288966504337</v>
+        <v>-22.22617365443643</v>
       </c>
       <c r="F24">
-        <v>0.4814842637926909</v>
+        <v>0.7012526208576081</v>
       </c>
       <c r="G24">
-        <v>-7.342347543669565</v>
+        <v>-6.072207089345085</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-11.22043840580758</v>
       </c>
       <c r="E25">
-        <v>-24.31370960249231</v>
+        <v>-22.0404201791158</v>
       </c>
       <c r="F25">
-        <v>0.2824731371071237</v>
+        <v>0.4632253895001842</v>
       </c>
       <c r="G25">
-        <v>-6.272601031928248</v>
+        <v>-6.179806440462476</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-11.0078699338628</v>
       </c>
       <c r="E26">
-        <v>-23.67017268973628</v>
+        <v>-22.81708517074932</v>
       </c>
       <c r="F26">
-        <v>0.272849164621399</v>
+        <v>0.3635330293080693</v>
       </c>
       <c r="G26">
-        <v>-6.980408910406585</v>
+        <v>-6.428951476656947</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-10.77618468550488</v>
       </c>
       <c r="E27">
-        <v>-23.06931664450255</v>
+        <v>-23.12707733047039</v>
       </c>
       <c r="F27">
-        <v>0.06204539958957802</v>
+        <v>0.3662185964279453</v>
       </c>
       <c r="G27">
-        <v>-6.902273414588707</v>
+        <v>-6.324775229627162</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-10.54018296846649</v>
       </c>
       <c r="E28">
-        <v>-23.19651242243</v>
+        <v>-21.8254580464457</v>
       </c>
       <c r="F28">
-        <v>0.4559506669687989</v>
+        <v>0.4657113200759855</v>
       </c>
       <c r="G28">
-        <v>-5.797842317232446</v>
+        <v>-6.245183093772004</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-10.32753735656741</v>
       </c>
       <c r="E29">
-        <v>-23.45319538613277</v>
+        <v>-22.53486614211729</v>
       </c>
       <c r="F29">
-        <v>0.1553469052690947</v>
+        <v>0.5872162507186169</v>
       </c>
       <c r="G29">
-        <v>-6.555838066086134</v>
+        <v>-6.74009309916535</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-10.13958784687652</v>
       </c>
       <c r="E30">
-        <v>-23.75070707148869</v>
+        <v>-21.86261870415264</v>
       </c>
       <c r="F30">
-        <v>0.04037199486273176</v>
+        <v>0.3241275919568968</v>
       </c>
       <c r="G30">
-        <v>-6.150792819356304</v>
+        <v>-6.226730112936107</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-9.986874094451524</v>
       </c>
       <c r="E31">
-        <v>-22.7992429831591</v>
+        <v>-21.35142644427078</v>
       </c>
       <c r="F31">
-        <v>-0.2413077135200177</v>
+        <v>0.4906948809444186</v>
       </c>
       <c r="G31">
-        <v>-6.622965997985935</v>
+        <v>-6.541271665713341</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-9.853388968700061</v>
       </c>
       <c r="E32">
-        <v>-22.81629721627198</v>
+        <v>-21.7994238493756</v>
       </c>
       <c r="F32">
-        <v>0.05066860167952961</v>
+        <v>0.1543023339741646</v>
       </c>
       <c r="G32">
-        <v>-6.093977236811332</v>
+        <v>-6.412935057337954</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-9.737055250273174</v>
       </c>
       <c r="E33">
-        <v>-20.37141485579683</v>
+        <v>-20.7781759765878</v>
       </c>
       <c r="F33">
-        <v>0.346561437959513</v>
+        <v>0.2023302476210771</v>
       </c>
       <c r="G33">
-        <v>-6.63121256692426</v>
+        <v>-6.448937240077528</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-9.614258190747307</v>
       </c>
       <c r="E34">
-        <v>-21.30719683863786</v>
+        <v>-20.35023065438894</v>
       </c>
       <c r="F34">
-        <v>0.4171292286366001</v>
+        <v>0.168323280633949</v>
       </c>
       <c r="G34">
-        <v>-4.849602758419</v>
+        <v>-5.670836548163845</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-9.481552551691744</v>
       </c>
       <c r="E35">
-        <v>-21.57240691889708</v>
+        <v>-20.35939628578047</v>
       </c>
       <c r="F35">
-        <v>0.08471698703679768</v>
+        <v>0.1718430137284441</v>
       </c>
       <c r="G35">
-        <v>-7.21531860078219</v>
+        <v>-5.718296529014838</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-9.318745560055579</v>
       </c>
       <c r="E36">
-        <v>-21.05726130120652</v>
+        <v>-19.01618296799533</v>
       </c>
       <c r="F36">
-        <v>-0.1097480593422059</v>
+        <v>0.8327037589056533</v>
       </c>
       <c r="G36">
-        <v>-5.46386786213969</v>
+        <v>-6.131091762852101</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-9.129073076950652</v>
       </c>
       <c r="E37">
-        <v>-20.27601349387724</v>
+        <v>-19.70548011059886</v>
       </c>
       <c r="F37">
-        <v>0.09531677632302016</v>
+        <v>-0.05577909468241526</v>
       </c>
       <c r="G37">
-        <v>-5.997845615441975</v>
+        <v>-5.088051421976085</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-8.901339793861585</v>
       </c>
       <c r="E38">
-        <v>-21.36193250396857</v>
+        <v>-19.39619439282299</v>
       </c>
       <c r="F38">
-        <v>0.07220201231530275</v>
+        <v>0.1211444435749059</v>
       </c>
       <c r="G38">
-        <v>-5.81435531838233</v>
+        <v>-5.152640165447266</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-8.648752132025139</v>
       </c>
       <c r="E39">
-        <v>-19.85228870945353</v>
+        <v>-19.22600528266673</v>
       </c>
       <c r="F39">
-        <v>0.1030263917408752</v>
+        <v>0.3615582014197953</v>
       </c>
       <c r="G39">
-        <v>-6.654684334797693</v>
+        <v>-5.292365050477746</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-8.369604312911065</v>
       </c>
       <c r="E40">
-        <v>-17.62957328379468</v>
+        <v>-18.10761258546638</v>
       </c>
       <c r="F40">
-        <v>-0.4315754222690362</v>
+        <v>0.1470640596085025</v>
       </c>
       <c r="G40">
-        <v>-5.036797555937088</v>
+        <v>-5.01848692855938</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-8.084619025933675</v>
       </c>
       <c r="E41">
-        <v>-19.58071159473953</v>
+        <v>-17.8301982677565</v>
       </c>
       <c r="F41">
-        <v>-0.2196773838981171</v>
+        <v>-0.06995825951613439</v>
       </c>
       <c r="G41">
-        <v>-5.213322465182107</v>
+        <v>-5.467290966227296</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-7.798118589012842</v>
       </c>
       <c r="E42">
-        <v>-19.38448828751316</v>
+        <v>-17.5177109188572</v>
       </c>
       <c r="F42">
-        <v>-0.3138287945329061</v>
+        <v>0.01672541898241707</v>
       </c>
       <c r="G42">
-        <v>-5.300121658676258</v>
+        <v>-4.999447981163031</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-7.533612546949828</v>
       </c>
       <c r="E43">
-        <v>-17.7687966886865</v>
+        <v>-16.88474799290909</v>
       </c>
       <c r="F43">
-        <v>-0.332392508029643</v>
+        <v>0.0677661048733114</v>
       </c>
       <c r="G43">
-        <v>-5.282608872773514</v>
+        <v>-5.486035275070649</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-7.294472404861667</v>
       </c>
       <c r="E44">
-        <v>-18.87929625569147</v>
+        <v>-16.34327835581195</v>
       </c>
       <c r="F44">
-        <v>-0.3884539287489051</v>
+        <v>0.2441338086033542</v>
       </c>
       <c r="G44">
-        <v>-6.014474485685734</v>
+        <v>-4.805486428562672</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-7.098293516191537</v>
       </c>
       <c r="E45">
-        <v>-17.86151719399355</v>
+        <v>-16.83065989936147</v>
       </c>
       <c r="F45">
-        <v>-0.3609363919953084</v>
+        <v>-0.220383981292705</v>
       </c>
       <c r="G45">
-        <v>-5.422472800716643</v>
+        <v>-4.907312188259575</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-6.940754877761941</v>
       </c>
       <c r="E46">
-        <v>-17.02358647751025</v>
+        <v>-15.28700726504883</v>
       </c>
       <c r="F46">
-        <v>-0.7000070507788132</v>
+        <v>-0.152327800580906</v>
       </c>
       <c r="G46">
-        <v>-5.377508971202261</v>
+        <v>-5.020840726437801</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-6.829752709789351</v>
       </c>
       <c r="E47">
-        <v>-16.62260368955307</v>
+        <v>-15.08084848584963</v>
       </c>
       <c r="F47">
-        <v>-0.1330922811204987</v>
+        <v>-0.163462715209337</v>
       </c>
       <c r="G47">
-        <v>-5.792469301822209</v>
+        <v>-5.232990416230917</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-6.753877325044362</v>
       </c>
       <c r="E48">
-        <v>-15.06617170159077</v>
+        <v>-14.88835211273158</v>
       </c>
       <c r="F48">
-        <v>-0.5146076572560474</v>
+        <v>-0.1417495488471563</v>
       </c>
       <c r="G48">
-        <v>-5.749279924716877</v>
+        <v>-5.245921407107311</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-6.7123288015443</v>
       </c>
       <c r="E49">
-        <v>-14.761663523893</v>
+        <v>-14.48384617199643</v>
       </c>
       <c r="F49">
-        <v>-0.2515140282899104</v>
+        <v>-0.1405856926462231</v>
       </c>
       <c r="G49">
-        <v>-6.198146862750039</v>
+        <v>-5.131230867444799</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-6.692223797632171</v>
       </c>
       <c r="E50">
-        <v>-15.40104329750998</v>
+        <v>-13.91649630594545</v>
       </c>
       <c r="F50">
-        <v>-0.5360913658476526</v>
+        <v>-0.3911022193356551</v>
       </c>
       <c r="G50">
-        <v>-4.862206005287005</v>
+        <v>-5.858756355155036</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-6.6896439567421</v>
       </c>
       <c r="E51">
-        <v>-13.88460226350942</v>
+        <v>-14.36196682255399</v>
       </c>
       <c r="F51">
-        <v>-0.7628478303225865</v>
+        <v>-0.4940417797467441</v>
       </c>
       <c r="G51">
-        <v>-5.852277617534682</v>
+        <v>-5.359105648549453</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-6.696449399955099</v>
       </c>
       <c r="E52">
-        <v>-14.13669335456842</v>
+        <v>-13.39465760367155</v>
       </c>
       <c r="F52">
-        <v>-0.3414010035350876</v>
+        <v>-0.5403458608284308</v>
       </c>
       <c r="G52">
-        <v>-5.416023858006143</v>
+        <v>-5.13323043695052</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-6.710872118381619</v>
       </c>
       <c r="E53">
-        <v>-14.13897570546828</v>
+        <v>-13.04318462204023</v>
       </c>
       <c r="F53">
-        <v>-0.1836989024923261</v>
+        <v>-0.601389911475532</v>
       </c>
       <c r="G53">
-        <v>-6.224495494697099</v>
+        <v>-5.079480419574912</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-6.732994181102752</v>
       </c>
       <c r="E54">
-        <v>-13.5363218560535</v>
+        <v>-13.03456240752962</v>
       </c>
       <c r="F54">
-        <v>0.1020878514735033</v>
+        <v>-0.5438332875942168</v>
       </c>
       <c r="G54">
-        <v>-6.124331628860909</v>
+        <v>-5.263199144276767</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-6.764784567997732</v>
       </c>
       <c r="E55">
-        <v>-12.93416613877957</v>
+        <v>-12.62366678996964</v>
       </c>
       <c r="F55">
-        <v>-0.6031568191457034</v>
+        <v>-0.68650134864357</v>
       </c>
       <c r="G55">
-        <v>-6.441816256622555</v>
+        <v>-5.819950140343699</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-6.81335108272317</v>
       </c>
       <c r="E56">
-        <v>-13.00103811445084</v>
+        <v>-11.87417264238215</v>
       </c>
       <c r="F56">
-        <v>-0.3948273875460445</v>
+        <v>-0.3203207098686458</v>
       </c>
       <c r="G56">
-        <v>-6.481155469265715</v>
+        <v>-5.808839949513905</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-6.88010755034477</v>
       </c>
       <c r="E57">
-        <v>-14.39851613626989</v>
+        <v>-11.89589573219694</v>
       </c>
       <c r="F57">
-        <v>-0.698536698638844</v>
+        <v>-0.5272808501514771</v>
       </c>
       <c r="G57">
-        <v>-7.175916487773784</v>
+        <v>-6.062815071650173</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-6.972143141965696</v>
       </c>
       <c r="E58">
-        <v>-13.84309879922913</v>
+        <v>-11.21045232097393</v>
       </c>
       <c r="F58">
-        <v>-0.3574647042101756</v>
+        <v>-0.6166144759715841</v>
       </c>
       <c r="G58">
-        <v>-6.699154893026723</v>
+        <v>-5.781090956803733</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-7.083904926121654</v>
       </c>
       <c r="E59">
-        <v>-12.50177385510518</v>
+        <v>-11.5559884731812</v>
       </c>
       <c r="F59">
-        <v>0.1063464882912956</v>
+        <v>-0.6119921858639629</v>
       </c>
       <c r="G59">
-        <v>-7.516760324860527</v>
+        <v>-6.481711640916313</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-7.218427194990451</v>
       </c>
       <c r="E60">
-        <v>-12.81355023358527</v>
+        <v>-11.5868636089655</v>
       </c>
       <c r="F60">
-        <v>-0.3255427379758938</v>
+        <v>-0.4262887815043697</v>
       </c>
       <c r="G60">
-        <v>-7.701621187773431</v>
+        <v>-6.140506954365788</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-7.362932422653162</v>
       </c>
       <c r="E61">
-        <v>-11.2029350541212</v>
+        <v>-10.60714184282804</v>
       </c>
       <c r="F61">
-        <v>-0.2942006289235718</v>
+        <v>-0.4375081896078862</v>
       </c>
       <c r="G61">
-        <v>-6.936355480915503</v>
+        <v>-6.653247558033649</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-7.517080059549205</v>
       </c>
       <c r="E62">
-        <v>-11.96755883336832</v>
+        <v>-11.73440582060941</v>
       </c>
       <c r="F62">
-        <v>-0.7077953610999341</v>
+        <v>-0.9525713016879657</v>
       </c>
       <c r="G62">
-        <v>-7.335153728212728</v>
+        <v>-7.280827675913288</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-7.664771702518094</v>
       </c>
       <c r="E63">
-        <v>-11.94273826733228</v>
+        <v>-10.32833275512379</v>
       </c>
       <c r="F63">
-        <v>-0.8589997482351363</v>
+        <v>-0.4421702413508419</v>
       </c>
       <c r="G63">
-        <v>-8.03467531120627</v>
+        <v>-6.896767977356898</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-7.804899951986429</v>
       </c>
       <c r="E64">
-        <v>-12.60251881635382</v>
+        <v>-10.19244683557563</v>
       </c>
       <c r="F64">
-        <v>-0.4731056220083894</v>
+        <v>-0.8552936324750113</v>
       </c>
       <c r="G64">
-        <v>-7.645646483795433</v>
+        <v>-7.229921417155915</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-7.921928865202483</v>
       </c>
       <c r="E65">
-        <v>-12.14911894175785</v>
+        <v>-11.12720538329093</v>
       </c>
       <c r="F65">
-        <v>-0.4648617096157287</v>
+        <v>-0.8259172392695324</v>
       </c>
       <c r="G65">
-        <v>-8.302346160238502</v>
+        <v>-7.42277062645508</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-8.016502640329008</v>
       </c>
       <c r="E66">
-        <v>-12.44927978440827</v>
+        <v>-11.42339022576261</v>
       </c>
       <c r="F66">
-        <v>-0.9627444817617463</v>
+        <v>-0.904118435563417</v>
       </c>
       <c r="G66">
-        <v>-6.726433788270318</v>
+        <v>-7.14486688116096</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-8.075901992035046</v>
       </c>
       <c r="E67">
-        <v>-11.87005625950917</v>
+        <v>-10.80520371050152</v>
       </c>
       <c r="F67">
-        <v>-0.9056467734215821</v>
+        <v>-1.152457184350889</v>
       </c>
       <c r="G67">
-        <v>-7.362475660548333</v>
+        <v>-7.065095975846681</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-8.104121295882157</v>
       </c>
       <c r="E68">
-        <v>-11.02566341061694</v>
+        <v>-10.4771746388079</v>
       </c>
       <c r="F68">
-        <v>-0.5616241343041417</v>
+        <v>-0.4714596559790268</v>
       </c>
       <c r="G68">
-        <v>-7.436148540979274</v>
+        <v>-7.434542926392727</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-8.092087465016007</v>
       </c>
       <c r="E69">
-        <v>-11.07406826928492</v>
+        <v>-11.25481778082708</v>
       </c>
       <c r="F69">
-        <v>-0.7081258796936512</v>
+        <v>-0.808813937503931</v>
       </c>
       <c r="G69">
-        <v>-8.136580523996114</v>
+        <v>-7.345442903748783</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-8.047704565951609</v>
       </c>
       <c r="E70">
-        <v>-10.92776233104511</v>
+        <v>-10.14650546676781</v>
       </c>
       <c r="F70">
-        <v>-0.9285105421062512</v>
+        <v>-0.8208923626041507</v>
       </c>
       <c r="G70">
-        <v>-7.433768258736539</v>
+        <v>-6.959890149154182</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-7.965742013978666</v>
       </c>
       <c r="E71">
-        <v>-12.72132333194505</v>
+        <v>-10.32224195758348</v>
       </c>
       <c r="F71">
-        <v>-0.7919069588127932</v>
+        <v>-1.077914058507767</v>
       </c>
       <c r="G71">
-        <v>-6.748031787368522</v>
+        <v>-7.418490091072802</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-7.857190365617659</v>
       </c>
       <c r="E72">
-        <v>-12.06464931609278</v>
+        <v>-10.73506217659671</v>
       </c>
       <c r="F72">
-        <v>-0.5681433857641739</v>
+        <v>-1.068791248300736</v>
       </c>
       <c r="G72">
-        <v>-7.384225944741345</v>
+        <v>-7.204403732139212</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-7.719101188352286</v>
       </c>
       <c r="E73">
-        <v>-11.51751002953803</v>
+        <v>-11.01365389754859</v>
       </c>
       <c r="F73">
-        <v>-0.9865451339789818</v>
+        <v>-0.9182876599883025</v>
       </c>
       <c r="G73">
-        <v>-7.71538974667126</v>
+        <v>-7.741887353167586</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-7.564121728753232</v>
       </c>
       <c r="E74">
-        <v>-14.01377698457822</v>
+        <v>-11.53913802139866</v>
       </c>
       <c r="F74">
-        <v>-1.084003387285746</v>
+        <v>-0.9627146605352456</v>
       </c>
       <c r="G74">
-        <v>-7.714959375751154</v>
+        <v>-7.535034536237305</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-7.39053883260065</v>
       </c>
       <c r="E75">
-        <v>-12.08718753122895</v>
+        <v>-11.11149610695832</v>
       </c>
       <c r="F75">
-        <v>-0.4952926145249714</v>
+        <v>-0.7804514659994788</v>
       </c>
       <c r="G75">
-        <v>-6.935428528164508</v>
+        <v>-7.055836379973339</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-7.21139342696917</v>
       </c>
       <c r="E76">
-        <v>-13.36306696899404</v>
+        <v>-11.95024194876299</v>
       </c>
       <c r="F76">
-        <v>-1.099663673035671</v>
+        <v>-1.147337045434185</v>
       </c>
       <c r="G76">
-        <v>-8.030394775823991</v>
+        <v>-6.804857301550112</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-7.023982034093352</v>
       </c>
       <c r="E77">
-        <v>-14.7354527163366</v>
+        <v>-12.9488248091424</v>
       </c>
       <c r="F77">
-        <v>-0.9204679229924708</v>
+        <v>-1.229926932228102</v>
       </c>
       <c r="G77">
-        <v>-6.771450586513327</v>
+        <v>-7.065797811501007</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-6.83920829962349</v>
       </c>
       <c r="E78">
-        <v>-13.27804034102603</v>
+        <v>-12.61887566446953</v>
       </c>
       <c r="F78">
-        <v>-1.212990132310463</v>
+        <v>-1.335630754662333</v>
       </c>
       <c r="G78">
-        <v>-8.082847059348204</v>
+        <v>-6.331442668343254</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-6.651729195105625</v>
       </c>
       <c r="E79">
-        <v>-14.62748936751973</v>
+        <v>-13.00338386398681</v>
       </c>
       <c r="F79">
-        <v>-1.600935296226542</v>
+        <v>-0.9821738391944088</v>
       </c>
       <c r="G79">
-        <v>-7.777005620248175</v>
+        <v>-6.692057083390525</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-6.468916112231319</v>
       </c>
       <c r="E80">
-        <v>-15.00953407717684</v>
+        <v>-13.26008494158561</v>
       </c>
       <c r="F80">
-        <v>-1.510335925014957</v>
+        <v>-1.364329543332321</v>
       </c>
       <c r="G80">
-        <v>-6.975148453544683</v>
+        <v>-7.299999045131208</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-6.282709185175678</v>
       </c>
       <c r="E81">
-        <v>-14.45792971525053</v>
+        <v>-14.75824905449121</v>
       </c>
       <c r="F81">
-        <v>-1.594325752719604</v>
+        <v>-1.64665703502406</v>
       </c>
       <c r="G81">
-        <v>-6.945615076788845</v>
+        <v>-7.369179515265357</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-6.096951178983865</v>
       </c>
       <c r="E82">
-        <v>-17.19231741903605</v>
+        <v>-15.02506221454914</v>
       </c>
       <c r="F82">
-        <v>-1.259863301797873</v>
+        <v>-1.544781098358166</v>
       </c>
       <c r="G82">
-        <v>-7.589297688171499</v>
+        <v>-7.436549116989526</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-5.904013909833763</v>
       </c>
       <c r="E83">
-        <v>-17.99771557824824</v>
+        <v>-15.96428583763601</v>
       </c>
       <c r="F83">
-        <v>-1.84519267882042</v>
+        <v>-1.554632043512258</v>
       </c>
       <c r="G83">
-        <v>-7.71575059613504</v>
+        <v>-6.977273823780895</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-5.706400722698531</v>
       </c>
       <c r="E84">
-        <v>-17.92846162524894</v>
+        <v>-17.01253247245753</v>
       </c>
       <c r="F84">
-        <v>-1.448232392459675</v>
+        <v>-1.547829490400468</v>
       </c>
       <c r="G84">
-        <v>-6.614050698848678</v>
+        <v>-6.829858541462689</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-5.500497323177002</v>
       </c>
       <c r="E85">
-        <v>-18.57564395958114</v>
+        <v>-17.80907746498472</v>
       </c>
       <c r="F85">
-        <v>-2.082648336669913</v>
+        <v>-1.768015344636396</v>
       </c>
       <c r="G85">
-        <v>-6.406568878265935</v>
+        <v>-6.34413198939528</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-5.290492417152715</v>
       </c>
       <c r="E86">
-        <v>-19.44221727416295</v>
+        <v>-18.9241824900555</v>
       </c>
       <c r="F86">
-        <v>-1.988502724606943</v>
+        <v>-1.984353432286321</v>
       </c>
       <c r="G86">
-        <v>-6.546985667314122</v>
+        <v>-7.282512743592777</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-5.079049335583754</v>
       </c>
       <c r="E87">
-        <v>-20.53039599278411</v>
+        <v>-20.05259670023481</v>
       </c>
       <c r="F87">
-        <v>-1.818106721483682</v>
+        <v>-1.753617490808338</v>
       </c>
       <c r="G87">
-        <v>-6.393594850297531</v>
+        <v>-6.509463944172023</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-4.873348225637352</v>
       </c>
       <c r="E88">
-        <v>-21.08715828660516</v>
+        <v>-21.50707915286242</v>
       </c>
       <c r="F88">
-        <v>-2.432772730076374</v>
+        <v>-1.825039328277711</v>
       </c>
       <c r="G88">
-        <v>-6.155493794022069</v>
+        <v>-6.7051635331805</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-4.683201043306363</v>
       </c>
       <c r="E89">
-        <v>-22.80699573066023</v>
+        <v>-22.61199058294193</v>
       </c>
       <c r="F89">
-        <v>-2.66927659378005</v>
+        <v>-2.00871157576564</v>
       </c>
       <c r="G89">
-        <v>-7.107470958749352</v>
+        <v>-6.969596668675325</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-4.518316278674936</v>
       </c>
       <c r="E90">
-        <v>-25.64370883312307</v>
+        <v>-24.20037095502834</v>
       </c>
       <c r="F90">
-        <v>-2.230521030111055</v>
+        <v>-2.08610345710699</v>
       </c>
       <c r="G90">
-        <v>-6.751875330739616</v>
+        <v>-5.929327254415679</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-4.394926449454245</v>
       </c>
       <c r="E91">
-        <v>-26.95110644998155</v>
+        <v>-26.5361533197107</v>
       </c>
       <c r="F91">
-        <v>-2.047441065316128</v>
+        <v>-1.860484341076099</v>
       </c>
       <c r="G91">
-        <v>-7.260792254309619</v>
+        <v>-6.702303221834569</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-4.323194266133156</v>
       </c>
       <c r="E92">
-        <v>-28.95011073118748</v>
+        <v>-27.97186524757652</v>
       </c>
       <c r="F92">
-        <v>-1.615834312333293</v>
+        <v>-2.070827533831964</v>
       </c>
       <c r="G92">
-        <v>-7.009160998415155</v>
+        <v>-6.504650410957923</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-4.322331589404977</v>
       </c>
       <c r="E93">
-        <v>-31.60549920590919</v>
+        <v>-28.92204777776194</v>
       </c>
       <c r="F93">
-        <v>-2.54417406350706</v>
+        <v>-2.124857797679562</v>
       </c>
       <c r="G93">
-        <v>-7.920279410096754</v>
+        <v>-7.198027621430576</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-4.397974471562688</v>
       </c>
       <c r="E94">
-        <v>-33.72214644912338</v>
+        <v>-32.17710130905337</v>
       </c>
       <c r="F94">
-        <v>-2.681248987852711</v>
+        <v>-1.843620437489907</v>
       </c>
       <c r="G94">
-        <v>-6.622188019784207</v>
+        <v>-6.489110710196583</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-4.563493922974629</v>
       </c>
       <c r="E95">
-        <v>-35.30117325814695</v>
+        <v>-34.14052084150703</v>
       </c>
       <c r="F95">
-        <v>-2.089739990005279</v>
+        <v>-2.066790899478122</v>
       </c>
       <c r="G95">
-        <v>-7.428590565513118</v>
+        <v>-7.188191990633402</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-4.821997715193313</v>
       </c>
       <c r="E96">
-        <v>-38.6143950380669</v>
+        <v>-36.72716708079231</v>
       </c>
       <c r="F96">
-        <v>-2.355310437505787</v>
+        <v>-1.876067588657564</v>
       </c>
       <c r="G96">
-        <v>-7.293007172952267</v>
+        <v>-7.345224407743191</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-5.172021974151161</v>
       </c>
       <c r="E97">
-        <v>-40.77822671620401</v>
+        <v>-38.43313380896188</v>
       </c>
       <c r="F97">
-        <v>-2.368334858180003</v>
+        <v>-2.368367164508713</v>
       </c>
       <c r="G97">
-        <v>-7.842498142651577</v>
+        <v>-7.174519437556212</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-5.620298621231974</v>
       </c>
       <c r="E98">
-        <v>-41.63584497343565</v>
+        <v>-40.49277435713051</v>
       </c>
       <c r="F98">
-        <v>-2.579731734272229</v>
+        <v>-2.394087972365637</v>
       </c>
       <c r="G98">
-        <v>-7.4686481665383</v>
+        <v>-8.033685458090027</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-6.139100484911468</v>
       </c>
       <c r="E99">
-        <v>-44.34163309962573</v>
+        <v>-43.65581835353409</v>
       </c>
       <c r="F99">
-        <v>-3.11913890758578</v>
+        <v>-2.070434059315634</v>
       </c>
       <c r="G99">
-        <v>-7.761548683125318</v>
+        <v>-7.872114283045897</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-6.750440958540051</v>
       </c>
       <c r="E100">
-        <v>-46.35964112200485</v>
+        <v>-45.74647668441826</v>
       </c>
       <c r="F100">
-        <v>-2.952391862871851</v>
+        <v>-2.318804286064413</v>
       </c>
       <c r="G100">
-        <v>-9.444063932003575</v>
+        <v>-8.051055890534583</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-7.376099157967729</v>
       </c>
       <c r="E101">
-        <v>-49.48171601406104</v>
+        <v>-47.9589690800048</v>
       </c>
       <c r="F101">
-        <v>-2.977701800496987</v>
+        <v>-2.508007542700834</v>
       </c>
       <c r="G101">
-        <v>-8.432622748299902</v>
+        <v>-8.230527185309553</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-8.104040477202057</v>
       </c>
       <c r="E102">
-        <v>-50.63489984494381</v>
+        <v>-49.74261045859094</v>
       </c>
       <c r="F102">
-        <v>-3.14405040049017</v>
+        <v>-2.547276299430544</v>
       </c>
       <c r="G102">
-        <v>-8.635658506223404</v>
+        <v>-8.293732120745318</v>
       </c>
     </row>
   </sheetData>
